--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-commentaire-non-code.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-commentaire-non-code.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="267">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -512,6 +512,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -698,6 +701,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -708,10 +714,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -724,6 +745,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -731,6 +761,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -738,6 +771,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -750,6 +786,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1132,7 +1174,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -4171,7 +4213,9 @@
       <c r="K30" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4242,10 +4286,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4279,7 +4323,7 @@
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>74</v>
@@ -4301,7 +4345,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>74</v>
@@ -4319,7 +4363,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4339,10 +4383,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4376,7 +4420,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4398,7 +4442,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4416,7 +4460,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4436,10 +4480,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4453,7 +4497,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4465,10 +4509,10 @@
         <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4519,7 +4563,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4539,10 +4583,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4556,7 +4600,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4565,13 +4609,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4622,7 +4666,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4642,10 +4686,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4743,10 +4787,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4775,7 +4819,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4787,7 +4831,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -4826,7 +4870,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4846,17 +4890,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
@@ -4878,7 +4922,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4890,7 +4934,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -4929,7 +4973,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4949,17 +4993,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4981,7 +5025,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4993,7 +5037,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5032,7 +5076,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5052,17 +5096,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5084,7 +5128,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5135,7 +5179,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5155,17 +5199,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>75</v>
@@ -5187,7 +5231,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5238,7 +5282,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5258,10 +5302,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5284,11 +5328,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5339,7 +5383,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5359,10 +5403,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5389,7 +5433,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5440,7 +5484,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5460,17 +5504,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5488,11 +5532,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5543,7 +5587,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5563,17 +5607,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5591,11 +5635,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5646,7 +5690,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5666,17 +5710,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5694,11 +5738,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5749,7 +5793,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5769,10 +5813,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5786,7 +5830,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5795,16 +5839,18 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -5852,7 +5898,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5872,10 +5918,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5889,7 +5935,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -5898,15 +5944,17 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -5955,7 +6003,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5975,10 +6023,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6001,12 +6049,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L48" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>74</v>
       </c>
@@ -6054,7 +6106,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6074,10 +6126,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6102,10 +6154,14 @@
       <c r="K49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>74</v>
       </c>
@@ -6133,7 +6189,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6151,7 +6207,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6171,10 +6227,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6197,12 +6253,18 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="N50" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>74</v>
       </c>
@@ -6250,7 +6312,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6270,10 +6332,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6296,12 +6358,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -6349,7 +6413,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6369,10 +6433,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6395,12 +6459,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>74</v>
       </c>
@@ -6448,7 +6514,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6468,10 +6534,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6494,7 +6560,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6547,7 +6613,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6567,10 +6633,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6593,12 +6659,16 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="L54" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>74</v>
       </c>
@@ -6646,7 +6716,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6666,10 +6736,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6767,10 +6837,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6868,10 +6938,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6969,10 +7039,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7070,10 +7140,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7173,10 +7243,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7276,10 +7346,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7379,10 +7449,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7482,10 +7552,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7583,10 +7653,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7613,7 +7683,7 @@
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7622,7 +7692,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>74</v>
@@ -7664,7 +7734,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7684,10 +7754,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7721,7 +7791,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -7763,7 +7833,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7783,10 +7853,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7809,7 +7879,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -7862,7 +7932,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
